--- a/Proyecto Interno/interno/output/lista_alimentos/lista_total_alimentos.xlsx
+++ b/Proyecto Interno/interno/output/lista_alimentos/lista_total_alimentos.xlsx
@@ -107,9 +107,6 @@
     <t xml:space="preserve">Bocachico criollo fresco</t>
   </si>
   <si>
-    <t xml:space="preserve">Bocadillo veleño</t>
-  </si>
-  <si>
     <t xml:space="preserve">Borojó</t>
   </si>
   <si>
@@ -354,6 +351,9 @@
   </si>
   <si>
     <t xml:space="preserve">Lulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandarina Arrayana</t>
   </si>
   <si>
     <t xml:space="preserve">Mandarina Oneco</t>

--- a/Proyecto Interno/interno/output/lista_alimentos/lista_total_alimentos.xlsx
+++ b/Proyecto Interno/interno/output/lista_alimentos/lista_total_alimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t xml:space="preserve">sipsa_name</t>
   </si>
@@ -32,6 +32,9 @@
     <t xml:space="preserve">Aguacate Hass</t>
   </si>
   <si>
+    <t xml:space="preserve">Aguacate común</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aguacate papelillo</t>
   </si>
   <si>
@@ -92,6 +95,12 @@
     <t xml:space="preserve">Bagre rayado en postas congelado</t>
   </si>
   <si>
+    <t xml:space="preserve">Bagre rayado entero congelado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagre rayado entero fresco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Banano bocadillo</t>
   </si>
   <si>
@@ -353,9 +362,6 @@
     <t xml:space="preserve">Lulo</t>
   </si>
   <si>
-    <t xml:space="preserve">Mandarina Arrayana</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mandarina Oneco</t>
   </si>
   <si>
@@ -479,6 +485,9 @@
     <t xml:space="preserve">Pierna pernil sin rabadilla</t>
   </si>
   <si>
+    <t xml:space="preserve">Piernas de pollo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pimentón</t>
   </si>
   <si>
@@ -509,6 +518,9 @@
     <t xml:space="preserve">Queso doble crema</t>
   </si>
   <si>
+    <t xml:space="preserve">Rabadillas de pollo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Remolacha</t>
   </si>
   <si>
@@ -557,6 +569,9 @@
     <t xml:space="preserve">Trucha en corte mariposa</t>
   </si>
   <si>
+    <t xml:space="preserve">Trucha entera fresca</t>
+  </si>
+  <si>
     <t xml:space="preserve">Uchuva con cáscara</t>
   </si>
   <si>
@@ -564,6 +579,9 @@
   </si>
   <si>
     <t xml:space="preserve">Uva Isabela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uva red globe nacional</t>
   </si>
   <si>
     <t xml:space="preserve">Uva roja</t>
@@ -1836,6 +1854,36 @@
         <v>186</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
